--- a/Team-Data/2011-12/2-5-2011-12.xlsx
+++ b/Team-Data/2011-12/2-5-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
         <v>5</v>
@@ -751,10 +818,10 @@
         <v>6</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ2" t="n">
         <v>19</v>
@@ -775,7 +842,7 @@
         <v>17</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
         <v>24</v>
@@ -790,7 +857,7 @@
         <v>15</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
         <v>4</v>
@@ -808,7 +875,7 @@
         <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -843,94 +910,94 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.545</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="J3" t="n">
         <v>74.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L3" t="n">
         <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.422</v>
+        <v>0.427</v>
       </c>
       <c r="O3" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P3" t="n">
         <v>20.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.763</v>
+        <v>0.757</v>
       </c>
       <c r="R3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="S3" t="n">
-        <v>30.1</v>
+        <v>29.7</v>
       </c>
       <c r="T3" t="n">
-        <v>38.9</v>
+        <v>38.6</v>
       </c>
       <c r="U3" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="V3" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="W3" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y3" t="n">
         <v>5.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF3" t="n">
         <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
         <v>24</v>
@@ -942,19 +1009,19 @@
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
         <v>20</v>
@@ -966,16 +1033,16 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
         <v>28</v>
@@ -987,7 +1054,7 @@
         <v>22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
         <v>16</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-13.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1115,7 +1182,7 @@
         <v>30</v>
       </c>
       <c r="AH4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
         <v>24</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1376,7 @@
         <v>6</v>
       </c>
       <c r="AL5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-3.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>20</v>
@@ -1533,13 +1600,13 @@
         <v>30</v>
       </c>
       <c r="AZ6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
         <v>10</v>
       </c>
       <c r="BB6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC6" t="n">
         <v>22</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1725,7 @@
         <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
         <v>21</v>
@@ -1679,7 +1746,7 @@
         <v>5</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>16</v>
@@ -1715,7 +1782,7 @@
         <v>5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>5.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1846,7 +1913,7 @@
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ8" t="n">
         <v>21</v>
@@ -1891,7 +1958,7 @@
         <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY8" t="n">
         <v>29</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2113,7 @@
         <v>15</v>
       </c>
       <c r="AO9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP9" t="n">
         <v>24</v>
@@ -2076,7 +2143,7 @@
         <v>30</v>
       </c>
       <c r="AY9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>1.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>14</v>
@@ -2392,7 +2459,7 @@
         <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ11" t="n">
         <v>1</v>
@@ -2422,7 +2489,7 @@
         <v>5</v>
       </c>
       <c r="AS11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT11" t="n">
         <v>4</v>
@@ -2440,7 +2507,7 @@
         <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ11" t="n">
         <v>16</v>
@@ -2452,7 +2519,7 @@
         <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2586,7 +2653,7 @@
         <v>22</v>
       </c>
       <c r="AM12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2859,7 @@
         <v>24</v>
       </c>
       <c r="AU13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
         <v>7</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>10</v>
@@ -2935,7 +3002,7 @@
         <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="n">
         <v>15</v>
@@ -2962,7 +3029,7 @@
         <v>12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>14</v>
@@ -2974,7 +3041,7 @@
         <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV14" t="n">
         <v>11</v>
@@ -2995,7 +3062,7 @@
         <v>14</v>
       </c>
       <c r="BB14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC14" t="n">
         <v>12</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -3027,64 +3094,64 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15" t="n">
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>0.522</v>
       </c>
       <c r="H15" t="n">
         <v>48.2</v>
       </c>
       <c r="I15" t="n">
-        <v>36.5</v>
+        <v>36.7</v>
       </c>
       <c r="J15" t="n">
-        <v>82.5</v>
+        <v>82.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.443</v>
+        <v>0.446</v>
       </c>
       <c r="L15" t="n">
         <v>3.5</v>
       </c>
       <c r="M15" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="N15" t="n">
-        <v>0.316</v>
+        <v>0.321</v>
       </c>
       <c r="O15" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="P15" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.742</v>
       </c>
       <c r="R15" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S15" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
       <c r="T15" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U15" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="V15" t="n">
         <v>15.3</v>
       </c>
       <c r="W15" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="X15" t="n">
         <v>5</v>
@@ -3093,40 +3160,40 @@
         <v>5.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
         <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL15" t="n">
         <v>30</v>
@@ -3135,7 +3202,7 @@
         <v>30</v>
       </c>
       <c r="AN15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
         <v>13</v>
@@ -3144,43 +3211,43 @@
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
         <v>9</v>
       </c>
       <c r="AS15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU15" t="n">
         <v>23</v>
       </c>
-      <c r="AT15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>24</v>
-      </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY15" t="n">
         <v>24</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB15" t="n">
         <v>18</v>
       </c>
-      <c r="BB15" t="n">
-        <v>20</v>
-      </c>
       <c r="BC15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -3209,88 +3276,88 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>0.75</v>
+        <v>0.739</v>
       </c>
       <c r="H16" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="I16" t="n">
-        <v>38.2</v>
+        <v>38.5</v>
       </c>
       <c r="J16" t="n">
-        <v>78.8</v>
+        <v>79.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.485</v>
+        <v>0.487</v>
       </c>
       <c r="L16" t="n">
         <v>5.8</v>
       </c>
       <c r="M16" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.393</v>
+        <v>0.395</v>
       </c>
       <c r="O16" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="P16" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.765</v>
+        <v>0.76</v>
       </c>
       <c r="R16" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>32.5</v>
       </c>
       <c r="T16" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U16" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="V16" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W16" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>103.2</v>
+        <v>103.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
         <v>2</v>
@@ -3302,16 +3369,16 @@
         <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
         <v>1</v>
       </c>
       <c r="AL16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="n">
         <v>24</v>
@@ -3320,10 +3387,10 @@
         <v>3</v>
       </c>
       <c r="AO16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ16" t="n">
         <v>11</v>
@@ -3335,28 +3402,28 @@
         <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AU16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW16" t="n">
         <v>9</v>
       </c>
       <c r="AX16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB16" t="n">
         <v>2</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3499,7 +3566,7 @@
         <v>11</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
         <v>22</v>
@@ -3520,7 +3587,7 @@
         <v>25</v>
       </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
         <v>9</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3718,16 @@
         <v>1.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH18" t="n">
         <v>24</v>
@@ -3684,7 +3751,7 @@
         <v>17</v>
       </c>
       <c r="AO18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP18" t="n">
         <v>5</v>
@@ -3726,7 +3793,7 @@
         <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -3839,10 +3906,10 @@
         <v>23</v>
       </c>
       <c r="AF19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH19" t="n">
         <v>21</v>
@@ -3851,7 +3918,7 @@
         <v>27</v>
       </c>
       <c r="AJ19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -3884,7 +3951,7 @@
         <v>28</v>
       </c>
       <c r="AU19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-5.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
         <v>21</v>
@@ -4036,7 +4103,7 @@
         <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL20" t="n">
         <v>29</v>
@@ -4081,7 +4148,7 @@
         <v>21</v>
       </c>
       <c r="AZ20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
@@ -4248,7 +4315,7 @@
         <v>19</v>
       </c>
       <c r="AU21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>4.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>1.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
         <v>8</v>
@@ -4573,7 +4640,7 @@
         <v>9</v>
       </c>
       <c r="AH23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI23" t="n">
         <v>29</v>
@@ -4636,7 +4703,7 @@
         <v>23</v>
       </c>
       <c r="BC23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>10.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF24" t="n">
         <v>4</v>
@@ -4758,7 +4825,7 @@
         <v>8</v>
       </c>
       <c r="AI24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ24" t="n">
         <v>6</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-4</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
         <v>20</v>
@@ -4985,7 +5052,7 @@
         <v>22</v>
       </c>
       <c r="AX25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY25" t="n">
         <v>2</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>6.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>10</v>
@@ -5119,7 +5186,7 @@
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
         <v>9</v>
@@ -5128,7 +5195,7 @@
         <v>5</v>
       </c>
       <c r="AK26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
         <v>17</v>
@@ -5137,7 +5204,7 @@
         <v>13</v>
       </c>
       <c r="AN26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO26" t="n">
         <v>9</v>
@@ -5170,7 +5237,7 @@
         <v>11</v>
       </c>
       <c r="AY26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ26" t="n">
         <v>19</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -5489,10 +5556,10 @@
         <v>5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>5</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E29" t="n">
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G29" t="n">
-        <v>0.32</v>
+        <v>0.333</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5593,7 +5660,7 @@
         <v>32.8</v>
       </c>
       <c r="J29" t="n">
-        <v>78.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="K29" t="n">
         <v>0.42</v>
@@ -5602,43 +5669,43 @@
         <v>5.5</v>
       </c>
       <c r="M29" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.32</v>
+        <v>0.323</v>
       </c>
       <c r="O29" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P29" t="n">
         <v>21</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.753</v>
+        <v>0.754</v>
       </c>
       <c r="R29" t="n">
         <v>10.4</v>
       </c>
       <c r="S29" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T29" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U29" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="V29" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W29" t="n">
         <v>6.5</v>
       </c>
       <c r="X29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y29" t="n">
         <v>5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>4.9</v>
       </c>
       <c r="Z29" t="n">
         <v>23.8</v>
@@ -5647,13 +5714,13 @@
         <v>18.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-6.4</v>
+        <v>-6.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5665,7 +5732,7 @@
         <v>25</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
         <v>30</v>
@@ -5683,7 +5750,7 @@
         <v>18</v>
       </c>
       <c r="AN29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO29" t="n">
         <v>19</v>
@@ -5698,25 +5765,25 @@
         <v>21</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
         <v>20</v>
       </c>
       <c r="AW29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX29" t="n">
         <v>15</v>
       </c>
       <c r="AY29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE30" t="n">
         <v>14</v>
@@ -5871,7 +5938,7 @@
         <v>5</v>
       </c>
       <c r="AP30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ30" t="n">
         <v>18</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-10.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-5-2011-12</t>
+          <t>2012-02-05</t>
         </is>
       </c>
     </row>
